--- a/02_Codigo/02_Tugboat/01_codes/EFF_Diesel_real.xlsx
+++ b/02_Codigo/02_Tugboat/01_codes/EFF_Diesel_real.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell PC\Desktop\Tesis Magister\02_Codigo\02_Tugboat\01_codes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desar\Documents\Tesis Magister\Tesis_Msc_LSZ\02_Codigo\02_Tugboat\01_codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25254680-3C9D-40B8-B721-BAC64D42D92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3763C973-2BFE-4701-AE85-575A295BB5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-4695" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30 min_1m" sheetId="4" r:id="rId1"/>
@@ -50,7 +50,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Leonardo Solis Zamora:</t>
         </r>
@@ -59,7 +59,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 sfc min del sistem propulsivo, o sea, se suma el sfc de cada motor.</t>
@@ -74,7 +74,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Leonardo Solis Zamora:</t>
         </r>
@@ -83,7 +83,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Potencia de ambos motores diesel.</t>
@@ -98,7 +98,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Leonardo Solis Zamora:</t>
         </r>
@@ -107,7 +107,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 SFC de ambos motores diesel</t>
@@ -122,7 +122,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Leonardo Solis Zamora:</t>
         </r>
@@ -131,7 +131,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Potencia de ambos motores diesel.</t>
@@ -146,7 +146,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Leonardo Solis Zamora:</t>
         </r>
@@ -155,7 +155,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 SFC de ambos motores diesel</t>
@@ -170,7 +170,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Leonardo Solis Zamora:</t>
         </r>
@@ -179,7 +179,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Potencia de ambos motores diesel.</t>
@@ -194,7 +194,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Leonardo Solis Zamora:</t>
         </r>
@@ -203,7 +203,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 SFC de ambos motores diesel</t>
@@ -228,7 +228,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Leonardo Solis Zamora:</t>
         </r>
@@ -237,7 +237,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 sfc corresponde a la suma de ambos motores.</t>
@@ -252,7 +252,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Leonardo Solis Zamora:</t>
         </r>
@@ -261,7 +261,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 sfc min del sistema de propulsión, por lo tanto, corresponde a la suma de los dos motores.</t>
@@ -276,7 +276,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Leonardo Solis Zamora:</t>
         </r>
@@ -285,7 +285,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 sfc corresponde a la suma de ambos motores.</t>
@@ -300,7 +300,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Leonardo Solis Zamora:</t>
         </r>
@@ -309,7 +309,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 sfc min del sistema de propulsión, por lo tanto, corresponde a la suma de los dos motores.</t>
@@ -324,7 +324,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Leonardo Solis Zamora:</t>
         </r>
@@ -333,7 +333,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 sfc corresponde a la suma de ambos motores.</t>
@@ -348,7 +348,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Leonardo Solis Zamora:</t>
         </r>
@@ -357,7 +357,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 sfc min del sistema de propulsión, por lo tanto, corresponde a la suma de los dos motores.</t>
@@ -529,19 +529,20 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -628,6 +629,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -637,7 +639,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -855,77 +856,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AJ1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" customWidth="1"/>
-    <col min="6" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="13" width="15.42578125" customWidth="1"/>
-    <col min="14" max="15" width="10.5703125" customWidth="1"/>
-    <col min="16" max="16" width="12.140625" customWidth="1"/>
-    <col min="17" max="17" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.54296875" customWidth="1"/>
+    <col min="2" max="4" width="15.453125" customWidth="1"/>
+    <col min="5" max="5" width="10.54296875" customWidth="1"/>
+    <col min="6" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="10" width="10.54296875" customWidth="1"/>
+    <col min="11" max="13" width="15.453125" customWidth="1"/>
+    <col min="14" max="15" width="10.54296875" customWidth="1"/>
+    <col min="16" max="16" width="12.1796875" customWidth="1"/>
+    <col min="17" max="17" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="6" bestFit="1" customWidth="1"/>
     <col min="21" max="25" width="12" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="10.5703125" customWidth="1"/>
-    <col min="28" max="28" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="35" width="10.5703125" customWidth="1"/>
+    <col min="26" max="27" width="10.54296875" customWidth="1"/>
+    <col min="28" max="28" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="35" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F5" s="21" t="s">
+    <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F5" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
-      <c r="Q5" s="22" t="s">
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="Q5" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="22"/>
-      <c r="V5" s="22"/>
-      <c r="W5" s="22"/>
-      <c r="X5" s="22"/>
-      <c r="Y5" s="22"/>
-      <c r="AB5" s="23" t="s">
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="23"/>
+      <c r="U5" s="23"/>
+      <c r="V5" s="23"/>
+      <c r="W5" s="23"/>
+      <c r="X5" s="23"/>
+      <c r="Y5" s="23"/>
+      <c r="AB5" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="AC5" s="22"/>
-      <c r="AD5" s="22"/>
-      <c r="AE5" s="22"/>
-      <c r="AF5" s="22"/>
-      <c r="AG5" s="22"/>
-      <c r="AH5" s="22"/>
-      <c r="AI5" s="22"/>
-      <c r="AJ5" s="22"/>
+      <c r="AC5" s="23"/>
+      <c r="AD5" s="23"/>
+      <c r="AE5" s="23"/>
+      <c r="AF5" s="23"/>
+      <c r="AG5" s="23"/>
+      <c r="AH5" s="23"/>
+      <c r="AI5" s="23"/>
+      <c r="AJ5" s="23"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -1023,7 +1024,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>832.5</v>
       </c>
@@ -1138,7 +1139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F8" s="1">
         <v>8.5000000000000107</v>
       </c>
@@ -1236,7 +1237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F9" s="1">
         <v>9.0000000000000107</v>
       </c>
@@ -1336,7 +1337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F10" s="1">
         <v>9.5000000000000195</v>
       </c>
@@ -1436,7 +1437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F11" s="1">
         <v>10</v>
       </c>
@@ -1538,7 +1539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F12" s="1">
         <v>10.5</v>
       </c>
@@ -1640,7 +1641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F13" s="1">
         <v>11</v>
       </c>
@@ -1744,7 +1745,7 @@
         <v>0.99146008499999994</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F14" s="1">
         <v>11.5</v>
       </c>
@@ -1848,7 +1849,7 @@
         <v>1.439548539</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F15" s="1">
         <v>12.000000000000099</v>
       </c>
@@ -1952,7 +1953,7 @@
         <v>2.4253314322500001</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F16" s="1">
         <v>12.500000000000099</v>
       </c>
@@ -2056,7 +2057,7 @@
         <v>1.439548539</v>
       </c>
     </row>
-    <row r="17" spans="6:36" x14ac:dyDescent="0.25">
+    <row r="17" spans="6:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F17" s="1">
         <v>13.000000000000099</v>
       </c>
@@ -2160,7 +2161,7 @@
         <v>1.439548539</v>
       </c>
     </row>
-    <row r="18" spans="6:36" x14ac:dyDescent="0.25">
+    <row r="18" spans="6:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F18" s="1">
         <v>13.500000000000099</v>
       </c>
@@ -2264,7 +2265,7 @@
         <v>0.99146008499999994</v>
       </c>
     </row>
-    <row r="19" spans="6:36" x14ac:dyDescent="0.25">
+    <row r="19" spans="6:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F19" s="1">
         <v>14.000000000000099</v>
       </c>
@@ -2366,7 +2367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="6:36" x14ac:dyDescent="0.25">
+    <row r="20" spans="6:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F20" s="1">
         <v>14.500000000000099</v>
       </c>
@@ -2468,7 +2469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F21" s="1">
         <v>15.000000000000099</v>
       </c>
@@ -2568,7 +2569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F22" s="1">
         <v>15.500000000000099</v>
       </c>
@@ -2668,7 +2669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F23" s="1">
         <v>16.000000000000099</v>
       </c>
@@ -2768,7 +2769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F24" s="1">
         <v>16.500000000000099</v>
       </c>
@@ -2868,7 +2869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F25" s="1">
         <v>17.000000000000099</v>
       </c>
@@ -2968,7 +2969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F26" s="1">
         <v>17.500000000000099</v>
       </c>
@@ -3068,7 +3069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F27" s="1">
         <v>18.000000000000099</v>
       </c>
@@ -3163,9 +3164,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F30" s="1" t="s">
         <v>15</v>
       </c>
@@ -3194,7 +3195,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F31" s="13" t="s">
         <v>21</v>
       </c>
@@ -3229,7 +3230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="6:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F32" s="13" t="s">
         <v>22</v>
       </c>
@@ -3264,7 +3265,7 @@
         <v>6.3015657869999995</v>
       </c>
     </row>
-    <row r="33" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F33" s="13" t="s">
         <v>23</v>
       </c>
@@ -3299,7 +3300,7 @@
         <v>2.4253314322500001</v>
       </c>
     </row>
-    <row r="34" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G34" s="2">
         <f t="shared" ref="G34:H34" si="20">SUM(G31:G33)</f>
         <v>5365.5438438438441</v>
@@ -3325,8 +3326,8 @@
         <v>8.7268972192499987</v>
       </c>
     </row>
-    <row r="35" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F36" s="1" t="s">
         <v>15</v>
       </c>
@@ -3355,7 +3356,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F37" s="13" t="s">
         <v>21</v>
       </c>
@@ -3390,7 +3391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F38" s="13" t="s">
         <v>22</v>
       </c>
@@ -3425,7 +3426,7 @@
         <v>0.72208548223758784</v>
       </c>
     </row>
-    <row r="39" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F39" s="13" t="s">
         <v>23</v>
       </c>
@@ -3460,7 +3461,7 @@
         <v>0.27791451776241227</v>
       </c>
     </row>
-    <row r="40" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G40" s="2">
         <f t="shared" ref="G40:H40" si="27">SUM(G37:G39)</f>
         <v>1</v>
@@ -3486,966 +3487,966 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="42" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="45" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="46" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="48" spans="6:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="F5:N5"/>
@@ -4461,62 +4462,62 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A2:AM1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="3" width="10.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="14" width="10.5703125" customWidth="1"/>
-    <col min="15" max="16" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" customWidth="1"/>
-    <col min="18" max="22" width="10.5703125" customWidth="1"/>
-    <col min="23" max="23" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="28" width="10.5703125" customWidth="1"/>
-    <col min="29" max="29" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="3" width="10.54296875" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="10.54296875" customWidth="1"/>
+    <col min="15" max="16" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7265625" customWidth="1"/>
+    <col min="18" max="22" width="10.54296875" customWidth="1"/>
+    <col min="23" max="23" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="10.54296875" customWidth="1"/>
+    <col min="29" max="29" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="23" t="s">
+    <row r="2" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D2" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="P2" s="23" t="s">
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="P2" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
-      <c r="X2" s="22"/>
-      <c r="Y2" s="22"/>
-      <c r="Z2" s="22"/>
-      <c r="AC2" s="23" t="s">
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AC2" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="22"/>
-      <c r="AE2" s="22"/>
-      <c r="AF2" s="22"/>
-      <c r="AG2" s="22"/>
-      <c r="AH2" s="22"/>
-      <c r="AI2" s="22"/>
-      <c r="AJ2" s="22"/>
-      <c r="AK2" s="22"/>
-      <c r="AL2" s="22"/>
-      <c r="AM2" s="22"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
+      <c r="AL2" s="23"/>
+      <c r="AM2" s="23"/>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -4575,7 +4576,7 @@
       <c r="V3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="W3" s="24" t="s">
+      <c r="W3" s="21" t="s">
         <v>33</v>
       </c>
       <c r="X3" s="1" t="s">
@@ -4608,7 +4609,7 @@
       <c r="AI3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AJ3" s="24" t="s">
+      <c r="AJ3" s="21" t="s">
         <v>33</v>
       </c>
       <c r="AK3" s="1" t="s">
@@ -4621,7 +4622,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>832500</v>
       </c>
@@ -4744,7 +4745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D5" s="1">
         <v>8.5</v>
       </c>
@@ -4847,7 +4848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D6" s="1">
         <v>9</v>
       </c>
@@ -4952,7 +4953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D7" s="1">
         <v>9.5</v>
       </c>
@@ -5057,7 +5058,7 @@
         <v>0.47106644865000002</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D8" s="1">
         <v>10</v>
       </c>
@@ -5119,7 +5120,7 @@
       </c>
       <c r="W8" s="1"/>
       <c r="Y8" s="1">
-        <f t="shared" ref="Y6:Y10" si="22">100*$K$4/S8</f>
+        <f t="shared" ref="Y8:Y9" si="22">100*$K$4/S8</f>
         <v>99.759284731774414</v>
       </c>
       <c r="Z8" s="1">
@@ -5161,7 +5162,7 @@
         <v>2.4253314322500001</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D9" s="1">
         <v>10.5</v>
       </c>
@@ -5266,7 +5267,7 @@
         <v>1.9147353412499999</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D10" s="2">
         <v>11</v>
       </c>
@@ -5370,7 +5371,7 @@
         <v>0.42079696417499995</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D11" s="4">
         <v>11.5</v>
       </c>
@@ -5472,7 +5473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D12" s="2">
         <v>12</v>
       </c>
@@ -5574,7 +5575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D13" s="4">
         <v>12.5</v>
       </c>
@@ -5675,7 +5676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D14" s="2">
         <v>13</v>
       </c>
@@ -5776,7 +5777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D15" s="4">
         <v>13.5</v>
       </c>
@@ -5877,7 +5878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D16" s="2">
         <v>13.995357142857101</v>
       </c>
@@ -5978,7 +5979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="4:39" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D17" s="4">
         <v>14.5</v>
       </c>
@@ -6079,7 +6080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="4:39" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D18" s="2">
         <v>14.994999999999999</v>
       </c>
@@ -6183,7 +6184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="4:39" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D19" s="4">
         <v>15.5</v>
       </c>
@@ -6287,7 +6288,7 @@
         <v>0.42079696417499995</v>
       </c>
     </row>
-    <row r="20" spans="4:39" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D20" s="2">
         <v>15.9946428571428</v>
       </c>
@@ -6349,7 +6350,7 @@
       </c>
       <c r="W20" s="1"/>
       <c r="Y20" s="1">
-        <f t="shared" ref="Y18:Y23" si="25">100*$K$4/S20</f>
+        <f t="shared" ref="Y20:Y21" si="25">100*$K$4/S20</f>
         <v>99.759284731774414</v>
       </c>
       <c r="Z20" s="1">
@@ -6391,7 +6392,7 @@
         <v>2.4253314322500001</v>
       </c>
     </row>
-    <row r="21" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D21" s="4">
         <v>16.5</v>
       </c>
@@ -6496,7 +6497,7 @@
         <v>1.792822038</v>
       </c>
     </row>
-    <row r="22" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D22" s="2">
         <v>16.994285714285699</v>
       </c>
@@ -6600,7 +6601,7 @@
         <v>0.51943056222374995</v>
       </c>
     </row>
-    <row r="23" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D23" s="4">
         <v>17.5</v>
       </c>
@@ -6704,7 +6705,7 @@
         <v>0.36897942071250001</v>
       </c>
     </row>
-    <row r="24" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D24" s="2">
         <v>17.993928571428601</v>
       </c>
@@ -6727,7 +6728,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="5">
-        <f t="shared" si="10"/>
+        <f>I24*$B$4+J23</f>
         <v>6384.5624624624625</v>
       </c>
       <c r="L24" s="1">
@@ -6805,7 +6806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="I25" s="5">
         <f>SUM(I4:I24)</f>
         <v>12769.124924924925</v>
@@ -6832,13 +6833,13 @@
         <v>10.759290603686251</v>
       </c>
     </row>
-    <row r="26" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="O26" s="13"/>
     </row>
-    <row r="27" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="O27" s="13"/>
     </row>
-    <row r="28" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D28" s="1" t="s">
         <v>19</v>
       </c>
@@ -6867,7 +6868,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D29" s="13" t="s">
         <v>30</v>
       </c>
@@ -6902,7 +6903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D30" s="13" t="s">
         <v>25</v>
       </c>
@@ -6938,7 +6939,7 @@
         <v>2.2010703599362498</v>
       </c>
     </row>
-    <row r="31" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D31" s="13" t="s">
         <v>26</v>
       </c>
@@ -6974,7 +6975,7 @@
         <v>8.5582202437500001</v>
       </c>
     </row>
-    <row r="32" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E32" s="6">
         <f t="shared" ref="E32:F32" si="27">SUM(E29:E31)</f>
         <v>6384.5624624624634</v>
@@ -7001,10 +7002,10 @@
         <v>10.759290603686249</v>
       </c>
     </row>
-    <row r="33" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D34" s="1" t="s">
         <v>19</v>
       </c>
@@ -7033,7 +7034,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D35" s="13" t="s">
         <v>30</v>
       </c>
@@ -7068,7 +7069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D36" s="13" t="s">
         <v>25</v>
       </c>
@@ -7103,7 +7104,7 @@
         <v>0.20457392973307545</v>
       </c>
     </row>
-    <row r="37" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D37" s="13" t="s">
         <v>26</v>
       </c>
@@ -7138,7 +7139,7 @@
         <v>0.79542607026692458</v>
       </c>
     </row>
-    <row r="38" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E38" s="6">
         <f>SUM(E35:E37)</f>
         <v>0.99999999999999989</v>
@@ -7164,968 +7165,968 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="41" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="42" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="45" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="46" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="48" spans="4:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="D2:M2"/>
